--- a/inferences/jesuita-entrada-Coimbra.xlsx
+++ b/inferences/jesuita-entrada-Coimbra.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="jesuita_entrada_Coimbra" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jesuita_entrada_Coimbra" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,11 @@
           <t>morte</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>extra_info</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -551,6 +556,11 @@
           <t>?</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -613,6 +623,11 @@
           <t>Goa</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -675,6 +690,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -737,6 +757,11 @@
           <t>Negapatam</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -799,6 +824,11 @@
           <t>Goa</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -861,6 +891,11 @@
           <t>[A caminho do Japão]</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -921,6 +956,11 @@
       <c r="N8" t="inlineStr">
         <is>
           <t>Macau</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -973,6 +1013,11 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1035,6 +1080,11 @@
           <t>[No mar, a caminho de Malaca]</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1097,6 +1147,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1157,6 +1212,11 @@
       <c r="N12" t="inlineStr">
         <is>
           <t>Goa (Colégio Novo)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -1209,6 +1269,11 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1271,6 +1336,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1333,6 +1403,11 @@
           <t>Hang-tcheou</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1395,6 +1470,11 @@
           <t>Japão</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1457,6 +1537,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1519,6 +1604,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1581,6 +1671,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1643,6 +1738,11 @@
           <t>Nagasaki</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>{'name': {'original': 'Bx Francisco Pacheco'}}</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1705,6 +1805,11 @@
           <t>Cantão</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1767,6 +1872,11 @@
           <t>Japão</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1829,6 +1939,11 @@
           <t>Edo</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1891,6 +2006,11 @@
           <t>Hangchow</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1953,6 +2073,11 @@
           <t>Nanquim</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2015,6 +2140,11 @@
           <t>Goa</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2077,6 +2207,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2139,6 +2274,11 @@
           <t>Foochow, Fukien</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>{'name': {'original': 'António de Gouvea'}}</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2201,6 +2341,11 @@
           <t>[Perto de Hainan]</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2263,6 +2408,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2325,6 +2475,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2387,6 +2542,11 @@
           <t>Pequim</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2449,6 +2609,11 @@
           <t>Costa da Cochinchina</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2509,6 +2674,11 @@
       <c r="N34" t="inlineStr">
         <is>
           <t>Macau</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -2561,6 +2731,11 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -2623,6 +2798,11 @@
           <t>Nanquim</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -2685,6 +2865,11 @@
           <t>Foochow (Fou-tcheou fou, Fukien)</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -2747,6 +2932,11 @@
           <t>[No mar, depois do Cabo da Boa Esperança]</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -2809,6 +2999,11 @@
           <t>Pequim</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -2869,6 +3064,11 @@
       <c r="N40" t="inlineStr">
         <is>
           <t>Goa</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -2913,6 +3113,11 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -2975,6 +3180,11 @@
           <t>Nanquim</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -3037,6 +3247,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3099,6 +3314,11 @@
           <t>Lisboa</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -3161,6 +3381,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -3223,6 +3448,11 @@
           <t>Coimbra</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -3285,6 +3515,11 @@
           <t>Macau</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -3347,6 +3582,11 @@
           <t>Tonquim</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -3407,6 +3647,11 @@
       <c r="N49" t="inlineStr">
         <is>
           <t>Macau</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -3459,6 +3704,11 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -3509,6 +3759,11 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -3571,6 +3826,11 @@
           <t>Pequim</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -3633,6 +3893,11 @@
           <t>Goa</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -3693,6 +3958,11 @@
       <c r="N54" t="inlineStr">
         <is>
           <t>?</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -3745,6 +4015,11 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -3805,6 +4080,11 @@
       <c r="N56" t="inlineStr">
         <is>
           <t>?</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -3857,6 +4137,11 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -3919,6 +4204,11 @@
           <t>Castel Gandolfo</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -3981,6 +4271,11 @@
           <t>Pequim</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -4041,6 +4336,11 @@
       <c r="N60" t="inlineStr">
         <is>
           <t>?</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>

--- a/inferences/jesuita-entrada-Coimbra.xlsx
+++ b/inferences/jesuita-entrada-Coimbra.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jesuita_entrada_Coimbra" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="jesuita_entrada_Coimbra" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
@@ -1216,34 +1216,34 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-gaspar</t>
+          <t>deh-francisco-vieira</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>886</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manuel Gaspar</t>
+          <t>Francisco Vieira</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1252,53 +1252,65 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>34</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>64</v>
+      </c>
+      <c r="M13" t="n">
+        <v>38</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Macau (colégio)</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-manuel-gaspar</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>353</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Manuel Gaspar</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1307,65 +1319,53 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>24</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1629</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>71</v>
-      </c>
-      <c r="M14" t="n">
-        <v>46</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Macau</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-da-rocha</t>
+          <t>deh-antonio-de-almeida</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>João da Rocha</t>
+          <t>António de Almeida</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1374,132 +1374,132 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="M15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Hang-tcheou</t>
+          <t>Shiuchow</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>705</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>1583</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>14</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1586</t>
-        </is>
-      </c>
       <c r="J16" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="M16" t="n">
         <v>46</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-soeiro</t>
+          <t>deh-joao-da-rocha</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>694</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>João Soeiro</t>
+          <t>João da Rocha</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1519,54 +1519,54 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M17" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Hang-tcheou</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>deh-diogo-correia-valente</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Diogo Correia Valente</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1575,60 +1575,60 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M18" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Japão</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-joao-soeiro</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>801</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>João Soeiro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1642,29 +1642,29 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1673,24 +1673,24 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-diogo-correia-valente</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Diogo Correia Valente</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1709,65 +1709,65 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="M20" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Nagasaki</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>{'name': {'original': 'Bx Francisco Pacheco'}}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-ferreira</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gaspar Ferreira</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>33</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>47</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1635</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>65</v>
+      </c>
+      <c r="M21" t="n">
         <v>17</v>
       </c>
-      <c r="H21" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1593</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>21</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>1649</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>78</v>
-      </c>
-      <c r="M21" t="n">
-        <v>56</v>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Cantão</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-fernandes</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>602</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sebastião Fernandes</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1858,50 +1858,50 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="L22" t="n">
+        <v>57</v>
+      </c>
+      <c r="M22" t="n">
         <v>34</v>
       </c>
-      <c r="M22" t="n">
-        <v>10</v>
-      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>Nagasaki</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name', 'original': 'Bx Francisco Pacheco'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-gaspar-ferreira</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>Gaspar Ferreira</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1910,65 +1910,65 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="M23" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Edo</t>
+          <t>Cantão</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-sebastiao-fernandes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Sebastião Fernandes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1977,65 +1977,65 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="M24" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Hangchow</t>
+          <t>Japão</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>deh-feliciano-da-silva</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Feliciano da Silva</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2044,65 +2044,65 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="M25" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Nanquim</t>
+          <t>Edo</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-andrade</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>254</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>António de Andrade</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2111,65 +2111,65 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="M26" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Hangchow</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>deh-simao-da-cunha</t>
+          <t>deh-feliciano-da-silva</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>772</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Simão da Cunha</t>
+          <t>Feliciano da Silva</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2178,65 +2178,65 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="M27" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Nanquim</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-gouvea</t>
+          <t>deh-antonio-de-andrade</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>António de Gouveia</t>
+          <t>António de Andrade</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2245,65 +2245,65 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="M28" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Foochow, Fukien</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>{'name': {'original': 'António de Gouvea'}}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-simao-da-cunha</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>232</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>Simão da Cunha</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2312,65 +2312,65 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="M29" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>[Perto de Hainan]</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-antonio-de-gouvea</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>António de Gouveia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2379,65 +2379,65 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="M30" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Foochow, Fukien</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name', 'original': 'António de Gouvea'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-da-maia</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sebastião da Maia</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2446,132 +2446,132 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H31" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="M31" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>[Perto de Hainan]</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>deh-gabriel-de-magalhaes</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>342</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gabriel de Magalhães</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>1589</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1625</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Coimbra</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H32" t="n">
         <v>8</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M32" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Pequim</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-sebastiao-da-maia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>510</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>Sebastião da Maia</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2580,65 +2580,65 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Costa da Cochinchina</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-da-fonseca</t>
+          <t>deh-gabriel-de-magalhaes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>506</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gonçalo da Fonseca</t>
+          <t>Gabriel de Magalhães</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2647,65 +2647,65 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H34" t="n">
         <v>8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="M34" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Pequim</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>deh-adriano-pestana</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>509</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Adriano Pestana</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2714,53 +2714,65 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>25</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1667</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>50</v>
+      </c>
+      <c r="M35" t="n">
+        <v>26</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Costa da Cochinchina</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-jorge</t>
+          <t>deh-goncalo-da-fonseca</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Manuel Jorge</t>
+          <t>Gonçalo da Fonseca</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2772,7 +2784,7 @@
         <v>16</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2780,54 +2792,54 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Nanquim</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-ferrao</t>
+          <t>deh-adriano-pestana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>631</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>André Ferrão</t>
+          <t>Adriano Pestana</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2836,65 +2848,53 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H37" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>31</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1661</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>36</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Foochow (Fou-tcheou fou, Fukien)</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>deh-afonso-aires</t>
+          <t>deh-manuel-jorge</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>420</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Afonso Aires</t>
+          <t>Manuel Jorge</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2903,65 +2903,65 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>[No mar, depois do Cabo da Boa Esperança]</t>
+          <t>Nanquim</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>deh-tome-pereira</t>
+          <t>deh-andre-ferrao</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>296</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tomé (Sancho) Pereira</t>
+          <t>André Ferrão</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2973,62 +2973,62 @@
         <v>15</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="M39" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Pequim</t>
+          <t>Foochow (Fou-tcheou fou, Fukien)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-carneiro</t>
+          <t>deh-afonso-aires</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>André Carneiro</t>
+          <t>Afonso Aires</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3037,65 +3037,65 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H40" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="M40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>[No mar, depois do Cabo da Boa Esperança]</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-da-silva</t>
+          <t>deh-tome-pereira</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>627</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>João da Silva</t>
+          <t>Tomé (Sancho) Pereira</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3104,45 +3104,65 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>21</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>63</v>
+      </c>
+      <c r="M41" t="n">
+        <v>42</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Pequim</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-da-silva</t>
+          <t>deh-andre-carneiro</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>António da Silva</t>
+          <t>André Carneiro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3151,10 +3171,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H42" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3162,54 +3182,54 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="M42" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Nanquim</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-mendes</t>
+          <t>deh-joao-da-silva</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>777</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manuel Mendes</t>
+          <t>João da Silva</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3218,65 +3238,45 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>17</v>
-      </c>
-      <c r="H43" t="n">
-        <v>7</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>24</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>84</v>
-      </c>
-      <c r="M43" t="n">
-        <v>60</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Macau</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-de-sa</t>
+          <t>deh-antonio-da-silva</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>768</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manuel de Sá</t>
+          <t>António da Silva</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3285,65 +3285,65 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M44" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Nanquim</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-i</t>
+          <t>deh-manuel-mendes</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>545</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>Manuel Mendes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3352,29 +3352,29 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="M45" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3383,34 +3383,34 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-manuel-de-sa</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>734</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>Manuel de Sá</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3419,65 +3419,65 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H46" t="n">
         <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M46" t="n">
         <v>48</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-osorio-i</t>
+          <t>deh-francisco-pinto-i</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>642</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manuel Osório</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3489,26 +3489,26 @@
         <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="M47" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3517,34 +3517,34 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>deh-estanislau-machado</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estanislau Machado</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3553,65 +3553,65 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="M48" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Tonquim</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-lopes-junior</t>
+          <t>deh-manuel-osorio-i</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>António Lopes, júnior</t>
+          <t>Manuel Osório</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3620,29 +3620,29 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3651,34 +3651,34 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>deh-leonardo-teixeira</t>
+          <t>deh-estanislau-machado</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>501</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Leonardo Teixeira</t>
+          <t>Estanislau Machado</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3687,53 +3687,65 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>62</v>
+      </c>
+      <c r="M50" t="n">
+        <v>42</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tonquim</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>deh-estevao-collasco</t>
+          <t>deh-antonio-lopes-junior</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>485</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Estêvão Collasco</t>
+          <t>António Lopes, júnior</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3745,7 +3757,7 @@
         <v>15</v>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3753,42 +3765,54 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>19</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1699</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>29</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Macau</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-magalhaes</t>
+          <t>deh-leonardo-teixeira</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>836</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>António de Magalhães</t>
+          <t>Leonardo Teixeira</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3804,58 +3828,46 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>19</v>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>57</v>
-      </c>
-      <c r="M52" t="n">
-        <v>38</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Pequim</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>deh-antao-dantas</t>
+          <t>deh-estevao-collasco</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>190</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Antão Dantas</t>
+          <t>Estêvão Collasco</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3864,65 +3876,53 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>19</v>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>1721</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>46</v>
-      </c>
-      <c r="M53" t="n">
-        <v>26</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Goa</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-ribeiro-senior</t>
+          <t>deh-antonio-de-magalhaes</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>504</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Manuel Ribeiro, sénior</t>
+          <t>António de Magalhães</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3931,22 +3931,22 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -3957,39 +3957,39 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Pequim</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-rodrigues</t>
+          <t>deh-antao-dantas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Matias Rodrigues</t>
+          <t>Antão Dantas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4001,50 +4001,62 @@
         <v>18</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>46</v>
+      </c>
+      <c r="M55" t="n">
+        <v>26</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-melo</t>
+          <t>deh-manuel-ribeiro-senior</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>679</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>António de Melo</t>
+          <t>Manuel Ribeiro, sénior</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4056,26 +4068,26 @@
         <v>17</v>
       </c>
       <c r="H56" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="M56" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4084,34 +4096,34 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-de-caldas</t>
+          <t>deh-matias-rodrigues</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>713</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Luís de Caldas</t>
+          <t>Matias Rodrigues</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4120,18 +4132,18 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H57" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -4139,34 +4151,34 @@
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-montanha-ii</t>
+          <t>deh-antonio-de-melo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>539</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>José Montanha</t>
+          <t>António de Melo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4175,65 +4187,65 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H58" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="M58" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Castel Gandolfo</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-gomes</t>
+          <t>deh-luis-de-caldas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>António Gomes</t>
+          <t>Luís de Caldas</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4242,105 +4254,227 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>20</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>44</v>
-      </c>
-      <c r="M59" t="n">
-        <v>23</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Pequim</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
+          <t>deh-jose-montanha-ii</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>José Montanha</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>13</v>
+      </c>
+      <c r="H60" t="n">
+        <v>21</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>34</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>56</v>
+      </c>
+      <c r="M60" t="n">
+        <v>22</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Castel Gandolfo</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>deh-antonio-gomes</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>António Gomes</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>18</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>20</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>44</v>
+      </c>
+      <c r="M61" t="n">
+        <v>23</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Pequim</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
           <t>deh-inacio-pires</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>651</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Inácio Pires</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>1724</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>1742</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
         <v>17</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H62" t="n">
         <v>8</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>1750</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J62" t="n">
         <v>25</v>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>1776</t>
         </is>
       </c>
-      <c r="L60" t="n">
+      <c r="L62" t="n">
         <v>51</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M62" t="n">
         <v>26</v>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>{}</t>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
         </is>
       </c>
     </row>

--- a/inferences/jesuita-entrada-Coimbra.xlsx
+++ b/inferences/jesuita-entrada-Coimbra.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>extra_info</t>
+          <t>jesuita-entrada.extra_info</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'já é padre'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Domingues &amp; O Neil, IV: 2645. MMHM:p.226', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 15600325 ou Coimbra, 25-03-1560 MMHM'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': 'Está no "Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579",Lus. 39 p.3v, nos estudantes de Filosofia do segundo curso', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Schutte, Monumenta historica japoniae I.,p.1180', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '"Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579" Lus. 39, 3v, estudante de filosofia, 1ºcurso', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Em Coimbra no ano de 1582 segundo a Carta Annua de 1623 BA', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 MMHM:p.94 (ARSI Japsin 35 13)', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segundo Dominguez &amp; O Neil, V.III,p.2961. Franco Imagem...Coimbra,II,4,c.36,p.575', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name', 'original': 'Bx Francisco Pacheco'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '([Schütte, 1975, p. 1321] Sebastião Vieira, nasc Castro de Aire, Lamego, E. Coimbra 3-2-1591', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segungo Dominguez, J. M., &amp; O’Neill, C. (2001) II, 1113', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': 'Franco, 1717, p. 375, Sweet, 20216, p.27 @wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Dehergne não especifica local, Brockey estudos Filosofia e Teologia em Coimbra', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name', 'original': 'António de Gouvea'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 (Franco, 1719, t.II, p. 612)', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 16090502 reentrou em 1611 não se sabe onde'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '[Adicionado a partir de Franco, Imagem...Coimbra, II, 522] @wikidata:Q45412', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'MMHM:p.8'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 """Franco, Imagem...Coimbra, v.2 p.616; Barbosa Machado, v.3"""', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': "@wikidata:Q45412 MMHM:p.205 (Sebastian da Maia, da Maya, d'Amaya)", 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segundo Louis Buglio 1688', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': "@wikidata:Q45412 MMHM:p.203 (Matias d'Amaia), Schutte, Monumenta historica japoniae I.1234", 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'original': '? Segundo Schütte, p.1174'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Ver Brockey, p.230 cit. Carta de A.P. a Viteleschi, de Coimbra, 26 Agosto 1640', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Brockey, cap.6 n.95', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 16630325'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 16690519'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 16931016 ou 16931021 ou 16930326'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 17051224'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>{'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>{'name': {'kleio_element_name': 'nome', 'kleio_element_class': 'name', 'entity_attr_name': 'name', 'entity_column_class': 'name'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'sex': {'kleio_element_name': 'sex', 'kleio_element_class': 'sex', 'entity_attr_name': 'sex', 'entity_column_class': 'sex'}}</t>
+          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>

--- a/inferences/jesuita-entrada-Coimbra.xlsx
+++ b/inferences/jesuita-entrada-Coimbra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,50 +451,65 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>nascimento</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>nascimento.wikidata</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>jesuita-entrada.date.year</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>jesuita-entrada</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>jesuita-entrada.wikidata</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>age_at_entrada</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>entrada_to_embarque</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>embarque.date.year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>age_at_embarque</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>morte.date.year</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>age_at_morte</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mission_time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>morte</t>
         </is>
@@ -523,31 +538,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>1542</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>19</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1579</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>56</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>56</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>?</t>
         </is>
       </c>
@@ -575,40 +601,55 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Q36433</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>1543</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>23</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>8</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>1551</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>31</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>1571</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>52</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>20</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Goa</t>
         </is>
@@ -637,40 +678,55 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>1543</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>23</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>1555</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>35</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1583</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>64</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>28</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -699,40 +755,55 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Villanueva de Barcarrota, diocese de Badajoz</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Q534483</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>1544</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>29</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1546</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>31</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1583</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>68</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>36</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Negapatam</t>
         </is>
@@ -761,40 +832,55 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Q273877</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>1544</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>15</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>11</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1555</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>26</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1572</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>44</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>17</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Goa</t>
         </is>
@@ -823,40 +909,55 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Vila Viçosa, diocese de Évora</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Q1013623</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>1549</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>21</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>19</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1568</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>40</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1573</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>46</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>[A caminho do Japão]</t>
         </is>
@@ -885,40 +986,51 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>1550</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>20</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1551</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>21</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>1582</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>52</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>31</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -947,32 +1059,43 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>1555</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>24</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>Q45412</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>24</v>
+      </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -997,40 +1120,55 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>13</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>29</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1585</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>42</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1598</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>55</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
         <v>12</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>[No mar, a caminho de Malaca]</t>
         </is>
@@ -1059,40 +1197,55 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Évora</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Q179948</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>20</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>16</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1576</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>36</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>1599</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>59</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
         <v>23</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -1121,40 +1274,55 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Q273877</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>1562</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>34</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>1596</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>49</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>1613</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="O12" t="n">
         <v>66</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
         <v>16</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Goa (Colégio Novo)</t>
         </is>
@@ -1183,40 +1351,55 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Vieira do Minho</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Q551109</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>1574</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>18</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>7</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>1581</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>25</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>1619</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
         <v>64</v>
       </c>
-      <c r="M13" t="n">
+      <c r="P13" t="n">
         <v>38</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Macau (colégio)</t>
         </is>
@@ -1245,32 +1428,47 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>São João Batista de Lobrigos, diocese do Porto</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Q774911</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>1575</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>21</v>
       </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>13</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>34</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1295,40 +1493,55 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Trancoso, diocese de Viseu</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Q686868</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>1576</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>18</v>
       </c>
-      <c r="H15" t="n">
+      <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>1584</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>26</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1591</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="O15" t="n">
         <v>34</v>
       </c>
-      <c r="M15" t="n">
+      <c r="P15" t="n">
         <v>7</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Shiuchow</t>
         </is>
@@ -1357,40 +1570,55 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Alcochete, diocese de Lisboa</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Q605319</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>1576</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>18</v>
       </c>
-      <c r="H16" t="n">
+      <c r="K16" t="n">
         <v>6</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>1583</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>24</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>1629</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>71</v>
       </c>
-      <c r="M16" t="n">
+      <c r="P16" t="n">
         <v>46</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -1419,40 +1647,55 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Santiago de Priscos, diocese de Braga</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Q1474626</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>1583</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>17</v>
       </c>
-      <c r="H17" t="n">
+      <c r="K17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="M17" t="n">
         <v>20</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>1623</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="O17" t="n">
         <v>57</v>
       </c>
-      <c r="M17" t="n">
+      <c r="P17" t="n">
         <v>36</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Hang-tcheou</t>
         </is>
@@ -1481,40 +1724,55 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Q597</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>1583</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>14</v>
       </c>
-      <c r="H18" t="n">
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
         <v>16</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1632</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="O18" t="n">
         <v>63</v>
       </c>
-      <c r="M18" t="n">
+      <c r="P18" t="n">
         <v>46</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Japão</t>
         </is>
@@ -1543,40 +1801,55 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Montemor-o-Velho, diocese de Coimbra</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Q45815</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>1584</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>18</v>
       </c>
-      <c r="H19" t="n">
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="M19" t="n">
         <v>19</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>1607</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="O19" t="n">
         <v>41</v>
       </c>
-      <c r="M19" t="n">
+      <c r="P19" t="n">
         <v>21</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -1605,40 +1878,55 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Q597</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>1584</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
         <v>15</v>
       </c>
-      <c r="H20" t="n">
+      <c r="K20" t="n">
         <v>34</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>1618</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="M20" t="n">
         <v>49</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>1633</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="O20" t="n">
         <v>65</v>
       </c>
-      <c r="M20" t="n">
+      <c r="P20" t="n">
         <v>15</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -1667,40 +1955,55 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Q597</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>1584</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>14</v>
       </c>
-      <c r="H21" t="n">
+      <c r="K21" t="n">
         <v>33</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="M21" t="n">
         <v>47</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>1635</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="O21" t="n">
         <v>65</v>
       </c>
-      <c r="M21" t="n">
+      <c r="P21" t="n">
         <v>17</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -1729,40 +2032,55 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Ponte de Lima, diocese de Braga</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Q490180</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>17</v>
       </c>
-      <c r="H22" t="n">
+      <c r="K22" t="n">
         <v>6</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>1592</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="M22" t="n">
         <v>23</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>1626</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="O22" t="n">
         <v>57</v>
       </c>
-      <c r="M22" t="n">
+      <c r="P22" t="n">
         <v>34</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Nagasaki</t>
         </is>
@@ -1791,40 +2109,51 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Castrofornos, diocese de Viseu</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
         <v>17</v>
       </c>
-      <c r="H23" t="n">
+      <c r="K23" t="n">
         <v>4</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>1593</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="M23" t="n">
         <v>21</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>1649</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="O23" t="n">
         <v>78</v>
       </c>
-      <c r="M23" t="n">
+      <c r="P23" t="n">
         <v>56</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Cantão</t>
         </is>
@@ -1853,40 +2182,55 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Besteiros, diocese de Viseu</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Q154246</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>1591</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
         <v>17</v>
       </c>
-      <c r="H24" t="n">
+      <c r="K24" t="n">
         <v>6</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>1597</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="M24" t="n">
         <v>23</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>1607</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="O24" t="n">
         <v>34</v>
       </c>
-      <c r="M24" t="n">
+      <c r="P24" t="n">
         <v>10</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Japão</t>
         </is>
@@ -1915,40 +2259,55 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Castro Daire, diocese de Lamego</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Q861199</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>1591</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
         <v>16</v>
       </c>
-      <c r="H25" t="n">
+      <c r="K25" t="n">
         <v>11</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>1602</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="M25" t="n">
         <v>27</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>1634</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="O25" t="n">
         <v>59</v>
       </c>
-      <c r="M25" t="n">
+      <c r="P25" t="n">
         <v>32</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
@@ -1977,40 +2336,55 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Q373720</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>1593</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
         <v>18</v>
       </c>
-      <c r="H26" t="n">
+      <c r="K26" t="n">
         <v>8</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>1601</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="M26" t="n">
         <v>26</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>1659</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="O26" t="n">
         <v>84</v>
       </c>
-      <c r="M26" t="n">
+      <c r="P26" t="n">
         <v>57</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Hangchow</t>
         </is>
@@ -2039,40 +2413,55 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Oliveira de Frades, diocese de Viseu</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Q861584</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>1593</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>14</v>
       </c>
-      <c r="H27" t="n">
+      <c r="K27" t="n">
         <v>7</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>1601</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="M27" t="n">
         <v>21</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>1614</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="O27" t="n">
         <v>34</v>
       </c>
-      <c r="M27" t="n">
+      <c r="P27" t="n">
         <v>13</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Nanquim</t>
         </is>
@@ -2101,40 +2490,55 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Oleiros, diocese de Portalegre</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Q1012719</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>1596</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
         <v>16</v>
       </c>
-      <c r="H28" t="n">
+      <c r="K28" t="n">
         <v>3</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="M28" t="n">
         <v>19</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>1634</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="O28" t="n">
         <v>53</v>
       </c>
-      <c r="M28" t="n">
+      <c r="P28" t="n">
         <v>33</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Goa</t>
         </is>
@@ -2163,40 +2567,55 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>1606</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
         <v>16</v>
       </c>
-      <c r="H29" t="n">
+      <c r="K29" t="n">
         <v>12</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>1618</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="M29" t="n">
         <v>28</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>1660</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="O29" t="n">
         <v>71</v>
       </c>
-      <c r="M29" t="n">
+      <c r="P29" t="n">
         <v>42</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -2225,40 +2644,51 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Casal, diocese de Viseu</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>1608</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
         <v>15</v>
       </c>
-      <c r="H30" t="n">
+      <c r="K30" t="n">
         <v>15</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>1623</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="M30" t="n">
         <v>30</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>1677</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="O30" t="n">
         <v>84</v>
       </c>
-      <c r="M30" t="n">
+      <c r="P30" t="n">
         <v>53</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Foochow, Fukien</t>
         </is>
@@ -2287,40 +2717,55 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Corvaceira, diocese de Viseu</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Q74384</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>1608</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
         <v>15</v>
       </c>
-      <c r="H31" t="n">
+      <c r="K31" t="n">
         <v>15</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>1623</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="M31" t="n">
         <v>30</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>1646</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="O31" t="n">
         <v>53</v>
       </c>
-      <c r="M31" t="n">
+      <c r="P31" t="n">
         <v>22</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>[Perto de Hainan]</t>
         </is>
@@ -2349,40 +2794,55 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Ilha do Faial, Açores</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Q657187</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
         <v>20</v>
       </c>
-      <c r="H32" t="n">
+      <c r="K32" t="n">
         <v>8</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>1618</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="M32" t="n">
         <v>28</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>1653</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="O32" t="n">
         <v>64</v>
       </c>
-      <c r="M32" t="n">
+      <c r="P32" t="n">
         <v>35</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -2411,40 +2871,55 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Q597</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
         <v>13</v>
       </c>
-      <c r="H33" t="n">
+      <c r="K33" t="n">
         <v>26</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>1637</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="M33" t="n">
         <v>39</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>1664</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="O33" t="n">
         <v>66</v>
       </c>
-      <c r="M33" t="n">
+      <c r="P33" t="n">
         <v>27</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -2473,40 +2948,55 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Pedrógão Grande, perto de Coimbra</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Q1013094</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>1625</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
         <v>15</v>
       </c>
-      <c r="H34" t="n">
+      <c r="K34" t="n">
         <v>8</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>1634</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="M34" t="n">
         <v>23</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>1677</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="O34" t="n">
         <v>66</v>
       </c>
-      <c r="M34" t="n">
+      <c r="P34" t="n">
         <v>43</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Pequim</t>
         </is>
@@ -2535,40 +3025,55 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Atalaia, diocese de Lisboa</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Q946933</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>1629</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
         <v>12</v>
       </c>
-      <c r="H35" t="n">
+      <c r="K35" t="n">
         <v>11</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>1640</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="M35" t="n">
         <v>23</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>1667</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="O35" t="n">
         <v>50</v>
       </c>
-      <c r="M35" t="n">
+      <c r="P35" t="n">
         <v>26</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Costa da Cochinchina</t>
         </is>
@@ -2597,40 +3102,55 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Vila Real, diocese de Braga</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Q503856</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>1634</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
         <v>16</v>
       </c>
-      <c r="H36" t="n">
+      <c r="K36" t="n">
         <v>8</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>1643</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="M36" t="n">
         <v>24</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>1662</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="O36" t="n">
         <v>44</v>
       </c>
-      <c r="M36" t="n">
+      <c r="P36" t="n">
         <v>19</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -2659,32 +3179,47 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Ilha de S. Miguel, Açores</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Q209036</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>1635</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
         <v>17</v>
       </c>
-      <c r="H37" t="n">
+      <c r="K37" t="n">
         <v>8</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>1643</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="M37" t="n">
         <v>25</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -2709,40 +3244,55 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>1638</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
         <v>16</v>
       </c>
-      <c r="H38" t="n">
+      <c r="K38" t="n">
         <v>5</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>1643</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="M38" t="n">
         <v>21</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>1677</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="O38" t="n">
         <v>56</v>
       </c>
-      <c r="M38" t="n">
+      <c r="P38" t="n">
         <v>34</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Nanquim</t>
         </is>
@@ -2771,40 +3321,55 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>Ceia, diocese de Coimbra</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Q1026336</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>1640</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
         <v>15</v>
       </c>
-      <c r="H39" t="n">
+      <c r="K39" t="n">
         <v>16</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>1657</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="M39" t="n">
         <v>31</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>1661</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="O39" t="n">
         <v>36</v>
       </c>
-      <c r="M39" t="n">
+      <c r="P39" t="n">
         <v>4</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Foochow (Fou-tcheou fou, Fukien)</t>
         </is>
@@ -2833,40 +3398,55 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Q273877</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>1649</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
         <v>19</v>
       </c>
-      <c r="H40" t="n">
+      <c r="K40" t="n">
         <v>7</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>1657</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="M40" t="n">
         <v>26</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>1657</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="O40" t="n">
         <v>27</v>
       </c>
-      <c r="M40" t="n">
+      <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>[No mar, depois do Cabo da Boa Esperança]</t>
         </is>
@@ -2895,40 +3475,55 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>S. Martinho do Vale, diocese de Braga</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Q950827</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>1661</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
         <v>15</v>
       </c>
-      <c r="H41" t="n">
+      <c r="K41" t="n">
         <v>5</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>1666</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="M41" t="n">
         <v>20</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>1708</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="O41" t="n">
         <v>63</v>
       </c>
-      <c r="M41" t="n">
+      <c r="P41" t="n">
         <v>42</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Pequim</t>
         </is>
@@ -2957,40 +3552,55 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Q36433</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>1664</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="H42" t="n">
+      <c r="K42" t="n">
         <v>31</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>1694</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="M42" t="n">
         <v>44</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>1709</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="O42" t="n">
         <v>58</v>
       </c>
-      <c r="M42" t="n">
+      <c r="P42" t="n">
         <v>14</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Goa</t>
         </is>
@@ -3019,24 +3629,39 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>São João de Areias</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Q93497</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>1668</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
         <v>21</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3061,40 +3686,55 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Q597</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>1669</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
         <v>15</v>
       </c>
-      <c r="H44" t="n">
+      <c r="K44" t="n">
         <v>25</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>1694</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="M44" t="n">
         <v>40</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>1726</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="O44" t="n">
         <v>72</v>
       </c>
-      <c r="M44" t="n">
+      <c r="P44" t="n">
         <v>31</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Nanquim</t>
         </is>
@@ -3123,40 +3763,55 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Soure, diocese de Coimbra</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Q543993</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>1673</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
         <v>17</v>
       </c>
-      <c r="H45" t="n">
+      <c r="K45" t="n">
         <v>7</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>1680</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="M45" t="n">
         <v>24</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>1741</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="O45" t="n">
         <v>84</v>
       </c>
-      <c r="M45" t="n">
+      <c r="P45" t="n">
         <v>60</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -3185,40 +3840,55 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Torre de Moncorvo, diocese de Braga</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Q551507</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>1675</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
         <v>16</v>
       </c>
-      <c r="H46" t="n">
+      <c r="K46" t="n">
         <v>5</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>1680</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="M46" t="n">
         <v>21</v>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>1728</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
         <v>69</v>
       </c>
-      <c r="M46" t="n">
+      <c r="P46" t="n">
         <v>48</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Lisboa</t>
         </is>
@@ -3247,40 +3917,55 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Lousã, diocese de Coimbra</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Q1006413</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>1677</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
         <v>14</v>
       </c>
-      <c r="H47" t="n">
+      <c r="K47" t="n">
         <v>4</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>1681</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="M47" t="n">
         <v>18</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>1731</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="O47" t="n">
         <v>68</v>
       </c>
-      <c r="M47" t="n">
+      <c r="P47" t="n">
         <v>49</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -3309,40 +3994,55 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>Carapito ou Mangualde, diocese de Viseu</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Q1035417</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>1677</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
         <v>19</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>5</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>1682</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="M48" t="n">
         <v>24</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>1730</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="O48" t="n">
         <v>72</v>
       </c>
-      <c r="M48" t="n">
+      <c r="P48" t="n">
         <v>48</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Coimbra</t>
         </is>
@@ -3371,40 +4071,55 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>Lamego</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Q117591</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>1678</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
         <v>14</v>
       </c>
-      <c r="H49" t="n">
+      <c r="K49" t="n">
         <v>8</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>1685</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="M49" t="n">
         <v>22</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>1710</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="O49" t="n">
         <v>47</v>
       </c>
-      <c r="M49" t="n">
+      <c r="P49" t="n">
         <v>25</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -3433,40 +4148,55 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Anobra, diocese de Coimbra</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Q567479</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>1681</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
         <v>13</v>
       </c>
-      <c r="H50" t="n">
+      <c r="K50" t="n">
         <v>7</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>1687</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="M50" t="n">
         <v>20</v>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>1729</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="O50" t="n">
         <v>62</v>
       </c>
-      <c r="M50" t="n">
+      <c r="P50" t="n">
         <v>42</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Tonquim</t>
         </is>
@@ -3495,40 +4225,55 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>1684</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
         <v>15</v>
       </c>
-      <c r="H51" t="n">
+      <c r="K51" t="n">
         <v>11</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>1695</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="M51" t="n">
         <v>26</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>1699</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="O51" t="n">
         <v>29</v>
       </c>
-      <c r="M51" t="n">
+      <c r="P51" t="n">
         <v>3</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
@@ -3557,32 +4302,47 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Q504580</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>1686</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
         <v>15</v>
       </c>
-      <c r="H52" t="n">
+      <c r="K52" t="n">
         <v>4</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>1690</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="M52" t="n">
         <v>19</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -3607,32 +4367,47 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>Semide, diocese de Coimbra</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Q770548</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>1692</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
         <v>15</v>
       </c>
-      <c r="H53" t="n">
+      <c r="K53" t="n">
         <v>4</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>1695</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="M53" t="n">
         <v>19</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -3657,40 +4432,51 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>Cortiços, diocese de Viseu</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>1692</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
         <v>15</v>
       </c>
-      <c r="H54" t="n">
+      <c r="K54" t="n">
         <v>4</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>1696</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="M54" t="n">
         <v>19</v>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>1735</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="O54" t="n">
         <v>57</v>
       </c>
-      <c r="M54" t="n">
+      <c r="P54" t="n">
         <v>38</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Pequim</t>
         </is>
@@ -3719,40 +4505,55 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Q36433</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>1693</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
         <v>18</v>
       </c>
-      <c r="H55" t="n">
+      <c r="K55" t="n">
         <v>1</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>1694</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="M55" t="n">
         <v>19</v>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>1721</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="O55" t="n">
         <v>46</v>
       </c>
-      <c r="M55" t="n">
+      <c r="P55" t="n">
         <v>26</v>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Goa</t>
         </is>
@@ -3781,40 +4582,55 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>Évora</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Q179948</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>1693</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
         <v>17</v>
       </c>
-      <c r="H56" t="n">
+      <c r="K56" t="n">
         <v>1</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>1695</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="M56" t="n">
         <v>18</v>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="O56" t="n">
         <v>57</v>
       </c>
-      <c r="M56" t="n">
+      <c r="P56" t="n">
         <v>38</v>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -3843,32 +4659,47 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>1694</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
         <v>18</v>
       </c>
-      <c r="H57" t="n">
+      <c r="K57" t="n">
         <v>2</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>1695</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="M57" t="n">
         <v>20</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -3893,40 +4724,55 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>Montemor-o-Velho, diocese de Coimbra</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Q45815</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>1699</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
         <v>17</v>
       </c>
-      <c r="H58" t="n">
+      <c r="K58" t="n">
         <v>16</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="M58" t="n">
         <v>33</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>1752</t>
         </is>
       </c>
-      <c r="L58" t="n">
+      <c r="O58" t="n">
         <v>70</v>
       </c>
-      <c r="M58" t="n">
+      <c r="P58" t="n">
         <v>37</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -3955,214 +4801,337 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>Valadares, diocese de Braga</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>1704</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
         <v>15</v>
       </c>
-      <c r="H59" t="n">
+      <c r="K59" t="n">
         <v>9</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>1714</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="M59" t="n">
         <v>24</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-montanha-ii</t>
+          <t>deh-estevao-lopes</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>487</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>José Montanha</t>
+          <t>Estêvão Lopes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Santo António da Terrugem, diocese de Elvas</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Q2257171</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>1708</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1721</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>13</v>
-      </c>
-      <c r="H60" t="n">
-        <v>21</v>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>Q45412</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>34</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>1764</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>56</v>
-      </c>
-      <c r="M60" t="n">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Castel Gandolfo</t>
+          <t>1766</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>73</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Lisboa (Forte de S. Julião)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-gomes</t>
+          <t>deh-jose-montanha-ii</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>559</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>António Gomes</t>
+          <t>José Montanha</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>18</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2</v>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>Q45412</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>20</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="K61" t="n">
+        <v>21</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
       </c>
       <c r="M61" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Pequim</t>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>56</v>
+      </c>
+      <c r="P61" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Castel Gandolfo</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
+          <t>deh-antonio-gomes</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>António Gomes</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Quintela da Lapa</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Q111798</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>18</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>20</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>44</v>
+      </c>
+      <c r="P62" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Pequim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
           <t>deh-inacio-pires</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>651</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Inácio Pires</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>1724</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Meãs do Campo, diocese de Coimbra</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Q1024746</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>1742</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Q45412</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
         <v>17</v>
       </c>
-      <c r="H62" t="n">
+      <c r="K63" t="n">
         <v>8</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>1750</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="M63" t="n">
         <v>25</v>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>1776</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="O63" t="n">
         <v>51</v>
       </c>
-      <c r="M62" t="n">
+      <c r="P63" t="n">
         <v>26</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>?</t>
         </is>
